--- a/Datos Experimentales/Data 24025.xlsx
+++ b/Datos Experimentales/Data 24025.xlsx
@@ -1,7 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltor\Documents\SB_Calibration_2025\Datos Experimentales\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17ACDBDD-73A5-4BCA-92C5-26E6656480F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Antecedentes_info" sheetId="1" r:id="rId1"/>
     <sheet name="Antecedentes" sheetId="2" r:id="rId2"/>
@@ -18,6 +28,7 @@
     <sheet name="Manual Densidades" sheetId="13" r:id="rId13"/>
     <sheet name="Winegrid densidad" sheetId="14" r:id="rId14"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -1044,11 +1055,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1077,14 +1085,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1409,10 +1426,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B117"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1420,7 +1438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1428,7 +1446,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1436,7 +1454,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1444,7 +1462,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1452,7 +1470,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1460,7 +1478,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1468,7 +1486,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1476,7 +1494,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1484,7 +1502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1492,7 +1510,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1500,7 +1518,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1508,7 +1526,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1516,7 +1534,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1524,7 +1542,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1532,7 +1550,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1540,7 +1558,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1548,7 +1566,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1556,7 +1574,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1564,7 +1582,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1572,7 +1590,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1580,7 +1598,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1588,7 +1606,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1596,7 +1614,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1604,7 +1622,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1612,7 +1630,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -1620,7 +1638,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1628,7 +1646,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1636,7 +1654,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1644,7 +1662,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1652,7 +1670,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1660,7 +1678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1668,7 +1686,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1676,7 +1694,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1684,7 +1702,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -1692,7 +1710,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -1700,7 +1718,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -1708,7 +1726,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -1716,7 +1734,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -1724,7 +1742,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -1732,7 +1750,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1740,7 +1758,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1748,7 +1766,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -1756,7 +1774,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -1764,7 +1782,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1772,7 +1790,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -1780,7 +1798,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1788,7 +1806,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>54</v>
       </c>
@@ -1796,7 +1814,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>55</v>
       </c>
@@ -1804,7 +1822,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>56</v>
       </c>
@@ -1812,7 +1830,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>57</v>
       </c>
@@ -1820,7 +1838,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>58</v>
       </c>
@@ -1828,7 +1846,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>59</v>
       </c>
@@ -1836,7 +1854,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -1844,7 +1862,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -1852,7 +1870,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -1860,7 +1878,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -1868,7 +1886,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -1876,7 +1894,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -1884,7 +1902,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -1892,7 +1910,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -1900,7 +1918,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -1908,7 +1926,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -1916,7 +1934,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -1924,7 +1942,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -1932,7 +1950,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -1940,7 +1958,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>75</v>
       </c>
@@ -1948,7 +1966,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>77</v>
       </c>
@@ -1956,7 +1974,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>78</v>
       </c>
@@ -1964,7 +1982,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>79</v>
       </c>
@@ -1972,7 +1990,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>80</v>
       </c>
@@ -1980,7 +1998,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>81</v>
       </c>
@@ -1988,7 +2006,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>82</v>
       </c>
@@ -1996,7 +2014,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -2004,7 +2022,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>84</v>
       </c>
@@ -2012,7 +2030,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>85</v>
       </c>
@@ -2020,7 +2038,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>86</v>
       </c>
@@ -2028,7 +2046,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>87</v>
       </c>
@@ -2036,7 +2054,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>88</v>
       </c>
@@ -2044,7 +2062,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>90</v>
       </c>
@@ -2052,7 +2070,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>91</v>
       </c>
@@ -2060,7 +2078,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>92</v>
       </c>
@@ -2068,7 +2086,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>94</v>
       </c>
@@ -2076,7 +2094,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>95</v>
       </c>
@@ -2084,7 +2102,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>96</v>
       </c>
@@ -2092,7 +2110,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>97</v>
       </c>
@@ -2100,7 +2118,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>98</v>
       </c>
@@ -2108,7 +2126,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>99</v>
       </c>
@@ -2116,7 +2134,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>100</v>
       </c>
@@ -2124,7 +2142,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>101</v>
       </c>
@@ -2132,7 +2150,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>102</v>
       </c>
@@ -2140,7 +2158,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>103</v>
       </c>
@@ -2148,7 +2166,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>104</v>
       </c>
@@ -2156,7 +2174,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>105</v>
       </c>
@@ -2164,7 +2182,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>106</v>
       </c>
@@ -2172,7 +2190,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>107</v>
       </c>
@@ -2180,7 +2198,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>108</v>
       </c>
@@ -2188,7 +2206,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>110</v>
       </c>
@@ -2196,7 +2214,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>111</v>
       </c>
@@ -2204,7 +2222,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>112</v>
       </c>
@@ -2212,7 +2230,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>113</v>
       </c>
@@ -2220,7 +2238,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>114</v>
       </c>
@@ -2228,7 +2246,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>115</v>
       </c>
@@ -2236,7 +2254,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>116</v>
       </c>
@@ -2244,7 +2262,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>117</v>
       </c>
@@ -2252,7 +2270,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>118</v>
       </c>
@@ -2260,7 +2278,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>119</v>
       </c>
@@ -2268,7 +2286,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>120</v>
       </c>
@@ -2276,7 +2294,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>121</v>
       </c>
@@ -2284,7 +2302,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>122</v>
       </c>
@@ -2292,7 +2310,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>123</v>
       </c>
@@ -2300,7 +2318,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>124</v>
       </c>
@@ -2308,7 +2326,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>126</v>
       </c>
@@ -2316,7 +2334,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>127</v>
       </c>
@@ -2324,7 +2342,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>128</v>
       </c>
@@ -2332,7 +2350,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>129</v>
       </c>
@@ -2340,7 +2358,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>130</v>
       </c>
@@ -2349,27 +2367,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B117"/>
+    <ignoredError sqref="A1:B117" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>280</v>
       </c>
@@ -2390,17 +2412,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
+    <ignoredError sqref="A1:F1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>285</v>
       </c>
@@ -2411,7 +2435,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>288</v>
       </c>
@@ -2422,7 +2446,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>289</v>
       </c>
@@ -2433,29 +2457,29 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>290</v>
       </c>
       <c r="B4">
-        <v>0.7229166666666667</v>
+        <v>0.72291666666666665</v>
       </c>
       <c r="C4">
         <v>15.5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>291</v>
       </c>
       <c r="B5">
-        <v>0.9729166666666667</v>
+        <v>0.97291666666666665</v>
       </c>
       <c r="C5">
         <v>17.5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>292</v>
       </c>
@@ -2466,7 +2490,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>293</v>
       </c>
@@ -2477,7 +2501,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>294</v>
       </c>
@@ -2488,7 +2512,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>295</v>
       </c>
@@ -2499,359 +2523,359 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>296</v>
       </c>
       <c r="B10">
-        <v>2.222916666666667</v>
+        <v>2.2229166666666669</v>
       </c>
       <c r="C10">
         <v>16.5</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>297</v>
       </c>
       <c r="B11">
-        <v>2.472916666666667</v>
+        <v>2.4729166666666669</v>
       </c>
       <c r="C11">
         <v>16.5</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>298</v>
       </c>
       <c r="B12">
-        <v>2.722916666666667</v>
+        <v>2.7229166666666669</v>
       </c>
       <c r="C12">
         <v>16.5</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>299</v>
       </c>
       <c r="B13">
-        <v>2.972916666666667</v>
+        <v>2.9729166666666669</v>
       </c>
       <c r="C13">
         <v>16.5</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>300</v>
       </c>
       <c r="B14">
-        <v>3.222916666666667</v>
+        <v>3.2229166666666669</v>
       </c>
       <c r="C14">
         <v>16.5</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>301</v>
       </c>
       <c r="B15">
-        <v>3.472916666666667</v>
+        <v>3.4729166666666669</v>
       </c>
       <c r="C15">
-        <v>16.4</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>302</v>
       </c>
       <c r="B16">
-        <v>3.722916666666667</v>
+        <v>3.7229166666666669</v>
       </c>
       <c r="C16">
         <v>16.5</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>303</v>
       </c>
       <c r="B17">
-        <v>3.972916666666667</v>
+        <v>3.9729166666666669</v>
       </c>
       <c r="C17">
         <v>16.5</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>304</v>
       </c>
       <c r="B18">
-        <v>4.222916666666666</v>
+        <v>4.2229166666666664</v>
       </c>
       <c r="C18">
         <v>16.8</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>305</v>
       </c>
       <c r="B19">
-        <v>4.472916666666666</v>
+        <v>4.4729166666666664</v>
       </c>
       <c r="C19">
         <v>16</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>306</v>
       </c>
       <c r="B20">
-        <v>4.722916666666666</v>
+        <v>4.7229166666666664</v>
       </c>
       <c r="C20">
         <v>16.3</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>307</v>
       </c>
       <c r="B21">
-        <v>4.972916666666666</v>
+        <v>4.9729166666666664</v>
       </c>
       <c r="C21">
         <v>16</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>308</v>
       </c>
       <c r="B22">
-        <v>5.222916666666666</v>
+        <v>5.2229166666666664</v>
       </c>
       <c r="C22">
         <v>15.8</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>309</v>
       </c>
       <c r="B23">
-        <v>5.472916666666666</v>
+        <v>5.4729166666666664</v>
       </c>
       <c r="C23">
         <v>16.3</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>310</v>
       </c>
       <c r="B24">
-        <v>5.722916666666666</v>
+        <v>5.7229166666666664</v>
       </c>
       <c r="C24">
         <v>16</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>311</v>
       </c>
       <c r="B25">
-        <v>5.972916666666666</v>
+        <v>5.9729166666666664</v>
       </c>
       <c r="C25">
         <v>16</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>312</v>
       </c>
       <c r="B26">
-        <v>6.222916666666666</v>
+        <v>6.2229166666666664</v>
       </c>
       <c r="C26">
         <v>16.5</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>313</v>
       </c>
       <c r="B27">
-        <v>6.472916666666666</v>
+        <v>6.4729166666666664</v>
       </c>
       <c r="C27">
-        <v>16.4</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>314</v>
       </c>
       <c r="B28">
-        <v>6.722916666666666</v>
+        <v>6.7229166666666664</v>
       </c>
       <c r="C28">
         <v>16</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>315</v>
       </c>
       <c r="B29">
-        <v>6.972916666666666</v>
+        <v>6.9729166666666664</v>
       </c>
       <c r="C29">
         <v>16.5</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>316</v>
       </c>
       <c r="B30">
-        <v>7.222916666666666</v>
+        <v>7.2229166666666664</v>
       </c>
       <c r="C30">
         <v>16.5</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>317</v>
       </c>
       <c r="B31">
-        <v>7.472916666666666</v>
+        <v>7.4729166666666664</v>
       </c>
       <c r="C31">
         <v>16.3</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>318</v>
       </c>
       <c r="B32">
-        <v>7.722916666666666</v>
+        <v>7.7229166666666664</v>
       </c>
       <c r="C32">
         <v>17</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>319</v>
       </c>
       <c r="B33">
-        <v>7.972916666666666</v>
+        <v>7.9729166666666664</v>
       </c>
       <c r="C33">
-        <v>17.1</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>320</v>
       </c>
       <c r="B34">
-        <v>8.222916666666666</v>
+        <v>8.2229166666666664</v>
       </c>
       <c r="C34">
         <v>16</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>321</v>
       </c>
       <c r="B35">
-        <v>8.472916666666666</v>
+        <v>8.4729166666666664</v>
       </c>
       <c r="C35">
         <v>17</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>322</v>
       </c>
       <c r="B36">
-        <v>8.722916666666666</v>
+        <v>8.7229166666666664</v>
       </c>
       <c r="C36">
         <v>16.5</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>323</v>
       </c>
       <c r="B37">
-        <v>8.972916666666666</v>
+        <v>8.9729166666666664</v>
       </c>
       <c r="C37">
         <v>16</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>324</v>
       </c>
       <c r="B38">
-        <v>9.222916666666666</v>
+        <v>9.2229166666666664</v>
       </c>
       <c r="C38">
         <v>16</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>325</v>
       </c>
       <c r="B39">
-        <v>9.472916666666666</v>
+        <v>9.4729166666666664</v>
       </c>
       <c r="C39">
-        <v>16.4</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>326</v>
       </c>
       <c r="B40">
-        <v>9.722916666666666</v>
+        <v>9.7229166666666664</v>
       </c>
       <c r="C40">
         <v>16.8</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>327</v>
       </c>
       <c r="B41">
-        <v>9.972916666666666</v>
+        <v>9.9729166666666664</v>
       </c>
       <c r="C41">
-        <v>16.4</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>328</v>
       </c>
@@ -2862,7 +2886,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>329</v>
       </c>
@@ -2870,10 +2894,10 @@
         <v>10.472916666666666</v>
       </c>
       <c r="C43">
-        <v>17.1</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>330</v>
       </c>
@@ -2884,7 +2908,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>331</v>
       </c>
@@ -2892,10 +2916,10 @@
         <v>10.972916666666666</v>
       </c>
       <c r="C45">
-        <v>17.1</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>332</v>
       </c>
@@ -2906,7 +2930,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>333</v>
       </c>
@@ -2917,7 +2941,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>334</v>
       </c>
@@ -2928,7 +2952,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>335</v>
       </c>
@@ -2936,21 +2960,23 @@
         <v>11.972916666666666</v>
       </c>
       <c r="C49">
-        <v>16.1</v>
+        <v>16.100000000000001</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C49"/>
+    <ignoredError sqref="A1:C49" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>285</v>
       </c>
@@ -2961,7 +2987,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>288</v>
       </c>
@@ -2972,7 +2998,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>289</v>
       </c>
@@ -2983,29 +3009,29 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>290</v>
       </c>
       <c r="B4">
-        <v>0.7229166666666667</v>
+        <v>0.72291666666666665</v>
       </c>
       <c r="C4">
         <v>1085</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>291</v>
       </c>
       <c r="B5">
-        <v>0.9729166666666667</v>
+        <v>0.97291666666666665</v>
       </c>
       <c r="C5">
         <v>1082</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>292</v>
       </c>
@@ -3016,7 +3042,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>293</v>
       </c>
@@ -3027,7 +3053,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>294</v>
       </c>
@@ -3038,7 +3064,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>295</v>
       </c>
@@ -3049,359 +3075,359 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>296</v>
       </c>
       <c r="B10">
-        <v>2.222916666666667</v>
+        <v>2.2229166666666669</v>
       </c>
       <c r="C10">
         <v>1065</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>297</v>
       </c>
       <c r="B11">
-        <v>2.472916666666667</v>
+        <v>2.4729166666666669</v>
       </c>
       <c r="C11">
         <v>1059</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>298</v>
       </c>
       <c r="B12">
-        <v>2.722916666666667</v>
+        <v>2.7229166666666669</v>
       </c>
       <c r="C12">
         <v>1057</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>299</v>
       </c>
       <c r="B13">
-        <v>2.972916666666667</v>
+        <v>2.9729166666666669</v>
       </c>
       <c r="C13">
         <v>1051</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>300</v>
       </c>
       <c r="B14">
-        <v>3.222916666666667</v>
+        <v>3.2229166666666669</v>
       </c>
       <c r="C14">
         <v>1049</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>301</v>
       </c>
       <c r="B15">
-        <v>3.472916666666667</v>
+        <v>3.4729166666666669</v>
       </c>
       <c r="C15">
         <v>1044</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>302</v>
       </c>
       <c r="B16">
-        <v>3.722916666666667</v>
+        <v>3.7229166666666669</v>
       </c>
       <c r="C16">
         <v>1038</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>303</v>
       </c>
       <c r="B17">
-        <v>3.972916666666667</v>
+        <v>3.9729166666666669</v>
       </c>
       <c r="C17">
         <v>1036</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>304</v>
       </c>
       <c r="B18">
-        <v>4.222916666666666</v>
+        <v>4.2229166666666664</v>
       </c>
       <c r="C18">
         <v>1035</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>305</v>
       </c>
       <c r="B19">
-        <v>4.472916666666666</v>
+        <v>4.4729166666666664</v>
       </c>
       <c r="C19">
         <v>1028</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>306</v>
       </c>
       <c r="B20">
-        <v>4.722916666666666</v>
+        <v>4.7229166666666664</v>
       </c>
       <c r="C20">
         <v>1025</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>307</v>
       </c>
       <c r="B21">
-        <v>4.972916666666666</v>
+        <v>4.9729166666666664</v>
       </c>
       <c r="C21">
         <v>1023</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>308</v>
       </c>
       <c r="B22">
-        <v>5.222916666666666</v>
+        <v>5.2229166666666664</v>
       </c>
       <c r="C22">
         <v>1021</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>309</v>
       </c>
       <c r="B23">
-        <v>5.472916666666666</v>
+        <v>5.4729166666666664</v>
       </c>
       <c r="C23">
         <v>1017</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>310</v>
       </c>
       <c r="B24">
-        <v>5.722916666666666</v>
+        <v>5.7229166666666664</v>
       </c>
       <c r="C24">
         <v>1014</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>311</v>
       </c>
       <c r="B25">
-        <v>5.972916666666666</v>
+        <v>5.9729166666666664</v>
       </c>
       <c r="C25">
         <v>1012</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>312</v>
       </c>
       <c r="B26">
-        <v>6.222916666666666</v>
+        <v>6.2229166666666664</v>
       </c>
       <c r="C26">
         <v>1012</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>313</v>
       </c>
       <c r="B27">
-        <v>6.472916666666666</v>
+        <v>6.4729166666666664</v>
       </c>
       <c r="C27">
         <v>1009</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>314</v>
       </c>
       <c r="B28">
-        <v>6.722916666666666</v>
+        <v>6.7229166666666664</v>
       </c>
       <c r="C28">
         <v>1009</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>315</v>
       </c>
       <c r="B29">
-        <v>6.972916666666666</v>
+        <v>6.9729166666666664</v>
       </c>
       <c r="C29">
         <v>1008</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>316</v>
       </c>
       <c r="B30">
-        <v>7.222916666666666</v>
+        <v>7.2229166666666664</v>
       </c>
       <c r="C30">
         <v>1006</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>317</v>
       </c>
       <c r="B31">
-        <v>7.472916666666666</v>
+        <v>7.4729166666666664</v>
       </c>
       <c r="C31">
         <v>1004</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>318</v>
       </c>
       <c r="B32">
-        <v>7.722916666666666</v>
+        <v>7.7229166666666664</v>
       </c>
       <c r="C32">
         <v>1003</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>319</v>
       </c>
       <c r="B33">
-        <v>7.972916666666666</v>
+        <v>7.9729166666666664</v>
       </c>
       <c r="C33">
         <v>1003</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>320</v>
       </c>
       <c r="B34">
-        <v>8.222916666666666</v>
+        <v>8.2229166666666664</v>
       </c>
       <c r="C34">
         <v>1002</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>321</v>
       </c>
       <c r="B35">
-        <v>8.472916666666666</v>
+        <v>8.4729166666666664</v>
       </c>
       <c r="C35">
         <v>1001</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>322</v>
       </c>
       <c r="B36">
-        <v>8.722916666666666</v>
+        <v>8.7229166666666664</v>
       </c>
       <c r="C36">
         <v>1001</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>323</v>
       </c>
       <c r="B37">
-        <v>8.972916666666666</v>
+        <v>8.9729166666666664</v>
       </c>
       <c r="C37">
         <v>1001</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>324</v>
       </c>
       <c r="B38">
-        <v>9.222916666666666</v>
+        <v>9.2229166666666664</v>
       </c>
       <c r="C38">
         <v>1000</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>325</v>
       </c>
       <c r="B39">
-        <v>9.472916666666666</v>
+        <v>9.4729166666666664</v>
       </c>
       <c r="C39">
         <v>997</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>326</v>
       </c>
       <c r="B40">
-        <v>9.722916666666666</v>
+        <v>9.7229166666666664</v>
       </c>
       <c r="C40">
         <v>997</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>327</v>
       </c>
       <c r="B41">
-        <v>9.972916666666666</v>
+        <v>9.9729166666666664</v>
       </c>
       <c r="C41">
         <v>996</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>328</v>
       </c>
@@ -3412,7 +3438,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>329</v>
       </c>
@@ -3423,7 +3449,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>330</v>
       </c>
@@ -3434,7 +3460,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>331</v>
       </c>
@@ -3445,7 +3471,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>332</v>
       </c>
@@ -3456,7 +3482,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>333</v>
       </c>
@@ -3467,7 +3493,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>334</v>
       </c>
@@ -3478,7 +3504,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>335</v>
       </c>
@@ -3490,17 +3516,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C49"/>
+    <ignoredError sqref="A1:C49" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>285</v>
       </c>
@@ -3524,17 +3552,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+    <ignoredError sqref="A1:G1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CZ2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:104" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -3848,7 +3878,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:104" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9845</v>
       </c>
@@ -3973,7 +4003,7 @@
         <v>145</v>
       </c>
       <c r="AS2">
-        <v>16.1</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="AT2">
         <v>12.6</v>
@@ -4072,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="BZ2">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="CA2">
         <v>0</v>
@@ -4114,7 +4144,7 @@
         <v>0</v>
       </c>
       <c r="CN2">
-        <v>0.048</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="CO2">
         <v>0</v>
@@ -4142,17 +4172,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:CZ2"/>
+    <ignoredError sqref="A1:CZ2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>161</v>
       </c>
@@ -4205,7 +4237,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9845</v>
       </c>
@@ -4234,7 +4266,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9845</v>
       </c>
@@ -4269,7 +4301,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9845</v>
       </c>
@@ -4298,7 +4330,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9845</v>
       </c>
@@ -4312,7 +4344,7 @@
         <v>186</v>
       </c>
       <c r="E5">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="F5" t="s">
         <v>182</v>
@@ -4348,7 +4380,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9845</v>
       </c>
@@ -4362,7 +4394,7 @@
         <v>186</v>
       </c>
       <c r="E6">
-        <v>0.048</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="F6" t="s">
         <v>182</v>
@@ -4398,7 +4430,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9845</v>
       </c>
@@ -4433,7 +4465,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9845</v>
       </c>
@@ -4480,7 +4512,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9845</v>
       </c>
@@ -4509,7 +4541,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9845</v>
       </c>
@@ -4544,7 +4576,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9845</v>
       </c>
@@ -4579,7 +4611,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9845</v>
       </c>
@@ -4615,17 +4647,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q12"/>
+    <ignoredError sqref="A1:Q12" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>161</v>
       </c>
@@ -4657,7 +4691,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9845</v>
       </c>
@@ -4689,7 +4723,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9845</v>
       </c>
@@ -4721,7 +4755,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9845</v>
       </c>
@@ -4754,27 +4788,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+    <ignoredError sqref="A1:J4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>161</v>
       </c>
@@ -4806,7 +4844,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9845</v>
       </c>
@@ -4839,17 +4877,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
+    <ignoredError sqref="A1:J2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>161</v>
       </c>
@@ -4866,7 +4906,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9845</v>
       </c>
@@ -4878,27 +4918,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError sqref="A1:E2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:P37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>161</v>
       </c>
@@ -4948,7 +4992,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9845</v>
       </c>
@@ -4961,7 +5005,7 @@
       <c r="D2">
         <v>6820</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>45373.77815972222</v>
       </c>
       <c r="F2" t="s">
@@ -4992,13 +5036,13 @@
         <v>244</v>
       </c>
       <c r="O2">
-        <v>7.5735</v>
+        <v>7.5735000000000001</v>
       </c>
       <c r="P2" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9845</v>
       </c>
@@ -5011,7 +5055,7 @@
       <c r="D3">
         <v>6820</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>45373.77815972222</v>
       </c>
       <c r="F3" t="s">
@@ -5042,13 +5086,13 @@
         <v>244</v>
       </c>
       <c r="O3">
-        <v>3.435</v>
+        <v>3.4350000000000001</v>
       </c>
       <c r="P3" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9845</v>
       </c>
@@ -5061,7 +5105,7 @@
       <c r="D4">
         <v>6820</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>45373.77815972222</v>
       </c>
       <c r="F4" t="s">
@@ -5098,7 +5142,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9845</v>
       </c>
@@ -5111,7 +5155,7 @@
       <c r="D5">
         <v>6820</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>45373.77815972222</v>
       </c>
       <c r="F5" t="s">
@@ -5148,7 +5192,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9845</v>
       </c>
@@ -5161,7 +5205,7 @@
       <c r="D6">
         <v>6820</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>45373.77815972222</v>
       </c>
       <c r="F6" t="s">
@@ -5198,7 +5242,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9845</v>
       </c>
@@ -5211,7 +5255,7 @@
       <c r="D7">
         <v>6820</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>45373.77815972222</v>
       </c>
       <c r="F7" t="s">
@@ -5248,7 +5292,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9845</v>
       </c>
@@ -5261,7 +5305,7 @@
       <c r="D8">
         <v>6820</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>45373.77815972222</v>
       </c>
       <c r="F8" t="s">
@@ -5298,7 +5342,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9845</v>
       </c>
@@ -5311,8 +5355,8 @@
       <c r="D9">
         <v>6886</v>
       </c>
-      <c r="E9">
-        <v>45376.65824074074</v>
+      <c r="E9" s="1">
+        <v>45373.65824074074</v>
       </c>
       <c r="F9" t="s">
         <v>134</v>
@@ -5342,13 +5386,13 @@
         <v>244</v>
       </c>
       <c r="O9">
-        <v>7.9101</v>
+        <v>7.9100999999999999</v>
       </c>
       <c r="P9" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9845</v>
       </c>
@@ -5361,8 +5405,8 @@
       <c r="D10">
         <v>6886</v>
       </c>
-      <c r="E10">
-        <v>45376.65824074074</v>
+      <c r="E10" s="1">
+        <v>45373.65824074074</v>
       </c>
       <c r="F10" t="s">
         <v>134</v>
@@ -5398,7 +5442,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9845</v>
       </c>
@@ -5411,8 +5455,8 @@
       <c r="D11">
         <v>6886</v>
       </c>
-      <c r="E11">
-        <v>45376.65824074074</v>
+      <c r="E11" s="1">
+        <v>45373.65824074074</v>
       </c>
       <c r="F11" t="s">
         <v>134</v>
@@ -5442,13 +5486,13 @@
         <v>244</v>
       </c>
       <c r="O11">
-        <v>20.4</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="P11" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9845</v>
       </c>
@@ -5461,8 +5505,8 @@
       <c r="D12">
         <v>6886</v>
       </c>
-      <c r="E12">
-        <v>45376.65824074074</v>
+      <c r="E12" s="1">
+        <v>45373.65824074074</v>
       </c>
       <c r="F12" t="s">
         <v>134</v>
@@ -5498,7 +5542,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9845</v>
       </c>
@@ -5511,8 +5555,8 @@
       <c r="D13">
         <v>6886</v>
       </c>
-      <c r="E13">
-        <v>45376.65824074074</v>
+      <c r="E13" s="1">
+        <v>45373.65824074074</v>
       </c>
       <c r="F13" t="s">
         <v>134</v>
@@ -5548,7 +5592,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>9845</v>
       </c>
@@ -5561,8 +5605,8 @@
       <c r="D14">
         <v>6886</v>
       </c>
-      <c r="E14">
-        <v>45376.65824074074</v>
+      <c r="E14" s="1">
+        <v>45373.65824074074</v>
       </c>
       <c r="F14" t="s">
         <v>134</v>
@@ -5598,7 +5642,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>9845</v>
       </c>
@@ -5611,8 +5655,8 @@
       <c r="D15">
         <v>6886</v>
       </c>
-      <c r="E15">
-        <v>45376.65824074074</v>
+      <c r="E15" s="1">
+        <v>45373.65824074074</v>
       </c>
       <c r="F15" t="s">
         <v>134</v>
@@ -5648,7 +5692,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>9845</v>
       </c>
@@ -5661,8 +5705,8 @@
       <c r="D16">
         <v>7168</v>
       </c>
-      <c r="E16">
-        <v>45384.85359953703</v>
+      <c r="E16" s="1">
+        <v>45384.853599537033</v>
       </c>
       <c r="F16" t="s">
         <v>134</v>
@@ -5698,7 +5742,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>9845</v>
       </c>
@@ -5711,8 +5755,8 @@
       <c r="D17">
         <v>7234</v>
       </c>
-      <c r="E17">
-        <v>45386.85878472222</v>
+      <c r="E17" s="1">
+        <v>45386.858784722222</v>
       </c>
       <c r="F17" t="s">
         <v>134</v>
@@ -5748,7 +5792,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>9845</v>
       </c>
@@ -5761,8 +5805,8 @@
       <c r="D18">
         <v>7287</v>
       </c>
-      <c r="E18">
-        <v>45387.75263888889</v>
+      <c r="E18" s="1">
+        <v>45387.752638888887</v>
       </c>
       <c r="F18" t="s">
         <v>134</v>
@@ -5798,7 +5842,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9845</v>
       </c>
@@ -5811,8 +5855,8 @@
       <c r="D19">
         <v>7287</v>
       </c>
-      <c r="E19">
-        <v>45387.75263888889</v>
+      <c r="E19" s="1">
+        <v>45387.752638888887</v>
       </c>
       <c r="F19" t="s">
         <v>134</v>
@@ -5848,7 +5892,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>9845</v>
       </c>
@@ -5861,8 +5905,8 @@
       <c r="D20">
         <v>7287</v>
       </c>
-      <c r="E20">
-        <v>45387.75263888889</v>
+      <c r="E20" s="1">
+        <v>45387.752638888887</v>
       </c>
       <c r="F20" t="s">
         <v>134</v>
@@ -5898,7 +5942,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>9845</v>
       </c>
@@ -5911,8 +5955,8 @@
       <c r="D21">
         <v>7287</v>
       </c>
-      <c r="E21">
-        <v>45387.75263888889</v>
+      <c r="E21" s="1">
+        <v>45387.752638888887</v>
       </c>
       <c r="F21" t="s">
         <v>134</v>
@@ -5948,7 +5992,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>9845</v>
       </c>
@@ -5961,8 +6005,8 @@
       <c r="D22">
         <v>7287</v>
       </c>
-      <c r="E22">
-        <v>45387.75263888889</v>
+      <c r="E22" s="1">
+        <v>45387.752638888887</v>
       </c>
       <c r="F22" t="s">
         <v>134</v>
@@ -5992,13 +6036,13 @@
         <v>244</v>
       </c>
       <c r="O22">
-        <v>0.202</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="P22" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>9845</v>
       </c>
@@ -6011,8 +6055,8 @@
       <c r="D23">
         <v>7287</v>
       </c>
-      <c r="E23">
-        <v>45387.75263888889</v>
+      <c r="E23" s="1">
+        <v>45387.752638888887</v>
       </c>
       <c r="F23" t="s">
         <v>134</v>
@@ -6048,7 +6092,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>9845</v>
       </c>
@@ -6061,8 +6105,8 @@
       <c r="D24">
         <v>7287</v>
       </c>
-      <c r="E24">
-        <v>45387.75263888889</v>
+      <c r="E24" s="1">
+        <v>45387.752638888887</v>
       </c>
       <c r="F24" t="s">
         <v>134</v>
@@ -6092,13 +6136,13 @@
         <v>244</v>
       </c>
       <c r="O24">
-        <v>0.202</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="P24" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9845</v>
       </c>
@@ -6111,8 +6155,8 @@
       <c r="D25">
         <v>7287</v>
       </c>
-      <c r="E25">
-        <v>45387.75263888889</v>
+      <c r="E25" s="1">
+        <v>45387.752638888887</v>
       </c>
       <c r="F25" t="s">
         <v>134</v>
@@ -6148,7 +6192,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>9845</v>
       </c>
@@ -6161,8 +6205,8 @@
       <c r="D26">
         <v>7287</v>
       </c>
-      <c r="E26">
-        <v>45387.75263888889</v>
+      <c r="E26" s="1">
+        <v>45387.752638888887</v>
       </c>
       <c r="F26" t="s">
         <v>134</v>
@@ -6198,7 +6242,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>9845</v>
       </c>
@@ -6211,8 +6255,8 @@
       <c r="D27">
         <v>7287</v>
       </c>
-      <c r="E27">
-        <v>45387.75263888889</v>
+      <c r="E27" s="1">
+        <v>45387.752638888887</v>
       </c>
       <c r="F27" t="s">
         <v>134</v>
@@ -6248,7 +6292,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>9845</v>
       </c>
@@ -6261,7 +6305,7 @@
       <c r="D28">
         <v>7461</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="1">
         <v>45392.81967592593</v>
       </c>
       <c r="F28" t="s">
@@ -6298,7 +6342,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>9845</v>
       </c>
@@ -6311,7 +6355,7 @@
       <c r="D29">
         <v>7461</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="1">
         <v>45392.81967592593</v>
       </c>
       <c r="F29" t="s">
@@ -6342,13 +6386,13 @@
         <v>244</v>
       </c>
       <c r="O29">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="P29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>9845</v>
       </c>
@@ -6361,7 +6405,7 @@
       <c r="D30">
         <v>7461</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="1">
         <v>45392.81967592593</v>
       </c>
       <c r="F30" t="s">
@@ -6398,7 +6442,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>9845</v>
       </c>
@@ -6411,7 +6455,7 @@
       <c r="D31">
         <v>7461</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="1">
         <v>45392.81967592593</v>
       </c>
       <c r="F31" t="s">
@@ -6448,7 +6492,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>9845</v>
       </c>
@@ -6461,7 +6505,7 @@
       <c r="D32">
         <v>7461</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="1">
         <v>45392.81967592593</v>
       </c>
       <c r="F32" t="s">
@@ -6492,13 +6536,13 @@
         <v>244</v>
       </c>
       <c r="O32">
-        <v>0.069</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="P32" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>9845</v>
       </c>
@@ -6511,7 +6555,7 @@
       <c r="D33">
         <v>7461</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="1">
         <v>45392.81967592593</v>
       </c>
       <c r="F33" t="s">
@@ -6548,7 +6592,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>9845</v>
       </c>
@@ -6561,7 +6605,7 @@
       <c r="D34">
         <v>7461</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="1">
         <v>45392.81967592593</v>
       </c>
       <c r="F34" t="s">
@@ -6592,13 +6636,13 @@
         <v>244</v>
       </c>
       <c r="O34">
-        <v>0.069</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="P34" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>9845</v>
       </c>
@@ -6611,7 +6655,7 @@
       <c r="D35">
         <v>7461</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="1">
         <v>45392.81967592593</v>
       </c>
       <c r="F35" t="s">
@@ -6648,7 +6692,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>9845</v>
       </c>
@@ -6661,7 +6705,7 @@
       <c r="D36">
         <v>7461</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="1">
         <v>45392.81967592593</v>
       </c>
       <c r="F36" t="s">
@@ -6698,7 +6742,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>9845</v>
       </c>
@@ -6711,7 +6755,7 @@
       <c r="D37">
         <v>7461</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="1">
         <v>45392.81967592593</v>
       </c>
       <c r="F37" t="s">
@@ -6749,8 +6793,9 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P37"/>
+    <ignoredError sqref="A1:P8 A16:P37 A9:D9 F9:P9 A10:D15 F10:P15" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>